--- a/public/downloads/DatalundSuiteSample.xlsx
+++ b/public/downloads/DatalundSuiteSample.xlsx
@@ -431,7 +431,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
@@ -450,7 +450,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Phase</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Start date</t>
+          <t>Start Date</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Estimated end</t>
+          <t>End Date</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Start Date</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>End Date</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -918,7 +918,7 @@
         <v>46198</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>46208</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9</v>
+        <v>90</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>46223</v>
       </c>
       <c r="E4" t="n">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>46270</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>20</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>46188</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46254</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4</v>
+        <v>40</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>46228</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>46239</v>
       </c>
       <c r="E10" t="n">
-        <v>0.15</v>
+        <v>15</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>46203</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>46244</v>
       </c>
       <c r="E13" t="n">
-        <v>0.85</v>
+        <v>85</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>46259</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3</v>
+        <v>30</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>46234</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7</v>
+        <v>70</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>46249</v>
       </c>
       <c r="E16" t="n">
-        <v>0.25</v>
+        <v>25</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>46296</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>46280</v>
       </c>
       <c r="E18" t="n">
-        <v>0.05</v>
+        <v>5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>46234</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>46249</v>
       </c>
       <c r="E20" t="n">
-        <v>0.55</v>
+        <v>55</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>46296</v>
       </c>
       <c r="E21" t="n">
-        <v>0.15</v>
+        <v>15</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>14</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>46266</v>
       </c>
       <c r="E24" t="n">
-        <v>0.15</v>
+        <v>15</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -1753,7 +1753,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Datalund suite sample — one workbook for Gantt, Resource Load, and Task List</t>
+          <t>DataLund suite sample — one workbook for Gantt, Resource Load, and Task List</t>
         </is>
       </c>
     </row>
@@ -1763,52 +1763,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. Power BI Desktop → Get data → Excel workbook → this file.</t>
+          <t>Shared field wells (same names across the suite)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. Load both Projects and Tasks. Relate Tasks[Project] → Projects[Project] (many-to-one).</t>
+          <t xml:space="preserve">  Task / Project · Start Date · End Date · Duration · Progress · Group · Resource / Project lead · RAG · Tooltips</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3. Import each .pbiviz (Visualizations … → Import a visual from a file).</t>
+          <t xml:space="preserve">  Progress is 0–100 here (visuals also accept 0–1). RAG: Red / Amber / Green (also Rød / Gul / Grønn).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  End Date or Duration is enough for timeline bars.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DataLund Task List (Projects sheet)</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Project → Project | RAG → RAG | Group → Phase | Project lead → Project lead</t>
+          <t>1. Power BI Desktop → Get data → Excel workbook → this file.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Progress → Progress | Start Date → Start date | End Date → Estimated end</t>
+          <t>2. Load both Projects and Tasks. Relate Tasks[Project] → Projects[Project] (many-to-one).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tooltips → Next milestone, Obstacles, Notes</t>
+          <t>3. Import each .pbiviz (Visualizations … → Import a visual from a file).</t>
         </is>
       </c>
     </row>
@@ -1818,62 +1818,100 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DataLund Gantt chart (Tasks sheet)</t>
+          <t>DataLund Task List (Projects sheet)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Task → Task | Start Date → Start | End Date → End | Duration → Duration</t>
+          <t xml:space="preserve">  Project → Project | RAG → RAG | Group → Group | Project lead → Project lead</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Progress → Progress | Group → Group | Resource → Resource</t>
+          <t xml:space="preserve">  Progress → Progress | Start Date → Start Date | End Date → End Date</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tooltips → Next milestone, Obstacles, Notes</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>DataLund Resource Load (Tasks sheet)</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Resource → Resource | Task → Task | Start Date → Start | End Date → End</t>
+          <t>DataLund Gantt chart (Tasks sheet)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Progress → Progress | Group → Group</t>
+          <t xml:space="preserve">  Task → Task | Start Date → Start Date | End Date → End Date | Duration → Duration</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Progress → Progress | Group → Group | Resource → Resource</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Tip: put Task List on the page and cross-filter Gantt + Resource Load from selected projects.</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Scope freeze is a zero-duration milestone. QA soak uses Duration instead of End.</t>
+          <t>DataLund Resource Load (Tasks sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Resource → Resource | Task → Task | Start Date → Start Date | End Date → End Date | Duration → Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Progress → Progress | Group → Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tip: put RAG on Tooltips if you want status on hover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Tip: put Task List on the page and cross-filter Gantt + Resource Load from selected projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Scope freeze is a zero-duration milestone. QA soak uses Duration instead of End Date.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/DatalundSuiteSample.xlsx
+++ b/public/downloads/DatalundSuiteSample.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Tasks" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Projects'!$A$1:$J$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Projects'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$G$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -559,15 +559,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="92" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="88" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -580,21 +579,19 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>A simple starter workbook for Task List, Gantt, and Resource Load</t>
+          <t>Seven columns. Replace the rows with your projects and tasks.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-    </row>
-    <row r="4" ht="22" customHeight="1">
+    </row>
+    <row r="4" ht="20" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Quick start</t>
@@ -604,158 +601,78 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>1. Import the visuals</t>
+          <t>1. Import the three .pbiviz files from datalund.no</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Download the suite zip from datalund.no, then in Power BI Desktop:</t>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2. Load Projects and Tasks — relate Tasks[Project] → Projects[Project]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Visualizations … → Import a visual from a file → pick each .pbiviz.</t>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3. Bind matching column names (see below)</t>
         </is>
       </c>
     </row>
     <row r="8"/>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>2. Load this workbook</t>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>What to maintain</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Home → Get data → Excel workbook → load Projects and Tasks.</t>
+          <t>Projects → DataLund Task List: Project, RAG, Group, Project lead, Progress, Start Date, End Date</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Relate Tasks[Project] → Projects[Project] (many-to-one).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>Tasks → Gantt + Resource Load: Task, Start Date, End Date, Progress, Group, Resource, Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Progress is 0–100. RAG is Red / Amber / Green (or Rød / Gul / Grønn).</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>3. Bind the same columns everywhere</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Minimum for Task List: Project (+ RAG and Progress look great).</t>
-        </is>
-      </c>
-    </row>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Same start and end date = milestone. Duration and Tooltips are optional later — not in this starter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Minimum for Gantt / Resource Load: Task, Start Date, and End Date or Duration.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Then add Progress, Group, and Resource / Project lead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+          <t>Put Task List on the page, click a project — Gantt and Resource Load follow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>https://datalund.no</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>4. Build one page</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Put Task List on the left. Click a project — Gantt and Resource Load follow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>What’s in the sheets</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Projects — portfolio rows for DataLund Task List (Lists-style names).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Tasks — assignment rows for DataLund Gantt and Resource Load.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Progress is 0–100. RAG is Red / Amber / Green (also Rød / Gul / Grønn).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Scope freeze is a milestone (same start and end). QA soak uses Duration instead of End Date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Make it yours</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Replace the sample rows with your projects and tasks. Keep the column headers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Same field names work across the whole DataLund suite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>https://datalund.no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Free Power BI visuals · support@datalund.no</t>
         </is>
@@ -763,11 +680,11 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -780,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -790,9 +707,6 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -831,21 +745,6 @@
           <t>End Date</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
-        <is>
-          <t>Next milestone</t>
-        </is>
-      </c>
-      <c r="I1" s="10" t="inlineStr">
-        <is>
-          <t>Obstacles</t>
-        </is>
-      </c>
-      <c r="J1" s="10" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
@@ -877,17 +776,6 @@
       <c r="G2" s="14" t="n">
         <v>46284</v>
       </c>
-      <c r="H2" s="11" t="inlineStr">
-        <is>
-          <t>FAT complete</t>
-        </is>
-      </c>
-      <c r="I2" s="11" t="inlineStr"/>
-      <c r="J2" s="11" t="inlineStr">
-        <is>
-          <t>On track for Q3</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
@@ -919,21 +807,6 @@
       <c r="G3" s="18" t="n">
         <v>46264</v>
       </c>
-      <c r="H3" s="15" t="inlineStr">
-        <is>
-          <t>Cable pull</t>
-        </is>
-      </c>
-      <c r="I3" s="15" t="inlineStr">
-        <is>
-          <t>Weather window</t>
-        </is>
-      </c>
-      <c r="J3" s="15" t="inlineStr">
-        <is>
-          <t>Watch supplier lead time</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -965,21 +838,6 @@
       <c r="G4" s="14" t="n">
         <v>46254</v>
       </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>Scope freeze</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>Budget overrun</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>Critical path slip</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -1011,17 +869,6 @@
       <c r="G5" s="18" t="n">
         <v>46259</v>
       </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>UAT</t>
-        </is>
-      </c>
-      <c r="I5" s="15" t="inlineStr"/>
-      <c r="J5" s="15" t="inlineStr">
-        <is>
-          <t>Near release</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -1053,20 +900,9 @@
       <c r="G6" s="14" t="n">
         <v>46424</v>
       </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>Permits</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>Replace these rows with your projects</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J6"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1078,18 +914,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -1110,32 +944,22 @@
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>Resource</t>
-        </is>
-      </c>
-      <c r="H1" s="10" t="inlineStr">
-        <is>
           <t>Project</t>
-        </is>
-      </c>
-      <c r="I1" s="10" t="inlineStr">
-        <is>
-          <t>RAG</t>
         </is>
       </c>
     </row>
@@ -1151,625 +975,368 @@
       <c r="C2" s="14" t="n">
         <v>46198</v>
       </c>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="13" t="n">
+      <c r="D2" s="13" t="n">
         <v>100</v>
       </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
       <c r="F2" s="11" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Ada Ng</t>
         </is>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
-          <t>Ada Ng</t>
-        </is>
-      </c>
-      <c r="H2" s="11" t="inlineStr">
-        <is>
           <t>North Sea Hub</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Wireframes</t>
+          <t>API design</t>
         </is>
       </c>
       <c r="B3" s="18" t="n">
-        <v>46193</v>
+        <v>46204</v>
       </c>
       <c r="C3" s="18" t="n">
-        <v>46208</v>
-      </c>
-      <c r="D3" s="15" t="n"/>
-      <c r="E3" s="17" t="n">
-        <v>90</v>
+        <v>46223</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
       </c>
       <c r="F3" s="15" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Sam Ortiz</t>
         </is>
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
-          <t>Jordan Lee</t>
-        </is>
-      </c>
-      <c r="H3" s="15" t="inlineStr">
-        <is>
           <t>North Sea Hub</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>API design</t>
+          <t>FAT prep</t>
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>46204</v>
+        <v>46254</v>
       </c>
       <c r="C4" s="14" t="n">
-        <v>46223</v>
-      </c>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="13" t="n">
-        <v>75</v>
+        <v>46270</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Ada Ng</t>
         </is>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>Sam Ortiz</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
           <t>North Sea Hub</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>FAT prep</t>
+          <t>Cable pull</t>
         </is>
       </c>
       <c r="B5" s="18" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C5" s="18" t="n">
         <v>46254</v>
       </c>
-      <c r="C5" s="18" t="n">
-        <v>46270</v>
-      </c>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="17" t="n">
-        <v>20</v>
+      <c r="D5" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Bo Berg</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>Ada Ng</t>
-        </is>
-      </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>North Sea Hub</t>
-        </is>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>Amber</t>
+          <t>Arctic Link</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Cable survey</t>
+          <t>Weather hold</t>
         </is>
       </c>
       <c r="B6" s="14" t="n">
-        <v>46154</v>
+        <v>46244</v>
       </c>
       <c r="C6" s="14" t="n">
-        <v>46188</v>
-      </c>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="13" t="n">
-        <v>100</v>
+        <v>46252</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Riley Chen</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>Bo Berg</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
           <t>Arctic Link</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>Cable pull</t>
+          <t>On-call week</t>
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>46204</v>
+        <v>46252</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>46254</v>
-      </c>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="17" t="n">
-        <v>40</v>
+        <v>46258</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Bo Berg</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>Bo Berg</t>
-        </is>
-      </c>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
           <t>Arctic Link</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>Amber</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Weather hold</t>
+          <t>Scope workshop</t>
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46244</v>
+        <v>46214</v>
       </c>
       <c r="C8" s="14" t="n">
-        <v>46252</v>
-      </c>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="13" t="n">
-        <v>0</v>
+        <v>46228</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Initiation</t>
+        </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Cara Diaz</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>Riley Chen</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>Arctic Link</t>
-        </is>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>Red</t>
+          <t>Yard Retrofit</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>On-call week</t>
+          <t>Scope freeze</t>
         </is>
       </c>
       <c r="B9" s="18" t="n">
-        <v>46252</v>
+        <v>46246</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>46258</v>
-      </c>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="17" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D9" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Initiation</t>
+        </is>
+      </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Cara Diaz</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>Bo Berg</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>Arctic Link</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
-        <is>
-          <t>Red</t>
+          <t>Yard Retrofit</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Scope workshop</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="B10" s="14" t="n">
-        <v>46214</v>
+        <v>46204</v>
       </c>
       <c r="C10" s="14" t="n">
-        <v>46228</v>
-      </c>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="13" t="n">
-        <v>50</v>
+        <v>46244</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Initiation</t>
+          <t>Sam Ortiz</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>Cara Diaz</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>Yard Retrofit</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>Amber</t>
+          <t>Digital Twin v2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Budget review</t>
+          <t>UAT</t>
         </is>
       </c>
       <c r="B11" s="18" t="n">
-        <v>46223</v>
+        <v>46245</v>
       </c>
       <c r="C11" s="18" t="n">
-        <v>46239</v>
-      </c>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="17" t="n">
-        <v>15</v>
+        <v>46259</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>Initiation</t>
+          <t>Ada Ng</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>Finn Olsen</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>Yard Retrofit</t>
-        </is>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>Red</t>
+          <t>Digital Twin v2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Scope freeze</t>
+          <t>Permit draft</t>
         </is>
       </c>
       <c r="B12" s="14" t="n">
-        <v>46246</v>
+        <v>46249</v>
       </c>
       <c r="C12" s="14" t="n">
-        <v>46246</v>
-      </c>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="13" t="n">
-        <v>0</v>
+        <v>46296</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Initiation</t>
+          <t>Finn Olsen</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>Cara Diaz</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Yard Retrofit</t>
-        </is>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>Red</t>
+          <t>Port Expansion</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Model training</t>
+          <t>Stakeholder map</t>
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>46124</v>
+        <v>46254</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>46203</v>
-      </c>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="17" t="n">
-        <v>100</v>
+        <v>46280</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Jordan Lee</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>Dan Okonkwo</t>
-        </is>
-      </c>
-      <c r="H13" s="15" t="inlineStr">
-        <is>
-          <t>Digital Twin v2</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>46204</v>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>46244</v>
-      </c>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="13" t="n">
-        <v>85</v>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>Sam Ortiz</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>Digital Twin v2</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>UAT</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="n">
-        <v>46245</v>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>46259</v>
-      </c>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="G15" s="15" t="inlineStr">
-        <is>
-          <t>Ada Ng</t>
-        </is>
-      </c>
-      <c r="H15" s="15" t="inlineStr">
-        <is>
-          <t>Digital Twin v2</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>Amber</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>QA soak</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n">
-        <v>46254</v>
-      </c>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>Riley Chen</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>Digital Twin v2</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Permit draft</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="n">
-        <v>46249</v>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>46296</v>
-      </c>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>Plan</t>
-        </is>
-      </c>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>Finn Olsen</t>
-        </is>
-      </c>
-      <c r="H17" s="15" t="inlineStr">
-        <is>
           <t>Port Expansion</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>Amber</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>Stakeholder map</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n">
-        <v>46254</v>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>46280</v>
-      </c>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Plan</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Jordan Lee</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>Port Expansion</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I18"/>
+  <autoFilter ref="A1:G13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/DatalundSuiteSample.xlsx
+++ b/public/downloads/DatalundSuiteSample.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Tasks" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Projects'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Projects'!$A$1:$F$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$G$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -559,10 +559,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="88" customWidth="1" min="1" max="1"/>
+    <col width="92" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -583,7 +583,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Seven columns. Replace the rows with your projects and tasks.</t>
+          <t>Two grains — portfolio vs assignments. Each attribute lives on one sheet.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -615,7 +615,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>3. Bind matching column names (see below)</t>
+          <t>3. Bind from the sheet that owns the column (see below)</t>
         </is>
       </c>
     </row>
@@ -623,56 +623,85 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>What to maintain</t>
+          <t>What to maintain (no duplicates)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Projects → DataLund Task List: Project, RAG, Group, Project lead, Progress, Start Date, End Date</t>
+          <t>Projects (Task List): Project · RAG · Project lead · Progress · Start Date · End Date</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Tasks → Gantt + Resource Load: Task, Start Date, End Date, Progress, Group, Resource, Project</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Progress is 0–100. RAG is Red / Amber / Green (or Rød / Gul / Grønn).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Same start and end date = milestone. Duration and Tooltips are optional later — not in this starter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>Tasks (Gantt + Resource Load): Task · Start Date · End Date · Progress · Group · Resource · Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>How the sheets connect</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Tasks[Project] is only the link to Projects — not a second project name to redesign.</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Put Task List on the page, click a project — Gantt and Resource Load follow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+          <t>Project lead = who owns the project. Resource = who does the task. Different people, different wells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Group lives on Tasks (Gantt sections). Do not copy Group onto Projects in this starter.</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>https://datalund.no</t>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Gantt Resource well → Tasks[Resource]. Never put Project in the Resource well.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Progress is 0–100. RAG is Red / Amber / Green (or Rød / Gul / Grønn).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Put Task List on the page, click a project — Gantt and Resource Load follow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>https://datalund.no</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Free Power BI visuals · support@datalund.no</t>
         </is>
@@ -684,7 +713,7 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -697,16 +726,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -722,25 +750,20 @@
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Project lead</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>Project lead</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Start Date</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>Start Date</t>
-        </is>
-      </c>
-      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
@@ -759,21 +782,16 @@
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
-        <is>
           <t>Ada Ng</t>
         </is>
       </c>
-      <c r="E2" s="13" t="n">
+      <c r="D2" s="13" t="n">
         <v>72</v>
       </c>
+      <c r="E2" s="14" t="n">
+        <v>46184</v>
+      </c>
       <c r="F2" s="14" t="n">
-        <v>46184</v>
-      </c>
-      <c r="G2" s="14" t="n">
         <v>46284</v>
       </c>
     </row>
@@ -790,21 +808,16 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
           <t>Bo Berg</t>
         </is>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="D3" s="17" t="n">
         <v>45</v>
       </c>
+      <c r="E3" s="18" t="n">
+        <v>46154</v>
+      </c>
       <c r="F3" s="18" t="n">
-        <v>46154</v>
-      </c>
-      <c r="G3" s="18" t="n">
         <v>46264</v>
       </c>
     </row>
@@ -821,21 +834,16 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Initiation</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
           <t>Cara Diaz</t>
         </is>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="D4" s="13" t="n">
         <v>18</v>
       </c>
+      <c r="E4" s="14" t="n">
+        <v>46214</v>
+      </c>
       <c r="F4" s="14" t="n">
-        <v>46214</v>
-      </c>
-      <c r="G4" s="14" t="n">
         <v>46254</v>
       </c>
     </row>
@@ -852,21 +860,16 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Build</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
           <t>Dan Okonkwo</t>
         </is>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="D5" s="17" t="n">
         <v>88</v>
       </c>
+      <c r="E5" s="18" t="n">
+        <v>46124</v>
+      </c>
       <c r="F5" s="18" t="n">
-        <v>46124</v>
-      </c>
-      <c r="G5" s="18" t="n">
         <v>46259</v>
       </c>
     </row>
@@ -883,26 +886,21 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Plan</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
           <t>Finn Olsen</t>
         </is>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="D6" s="13" t="n">
         <v>12</v>
       </c>
+      <c r="E6" s="14" t="n">
+        <v>46249</v>
+      </c>
       <c r="F6" s="14" t="n">
-        <v>46249</v>
-      </c>
-      <c r="G6" s="14" t="n">
         <v>46424</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:F6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/public/downloads/DatalundSuiteSample.xlsx
+++ b/public/downloads/DatalundSuiteSample.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Projects'!$A$1:$F$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$F$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="92" customWidth="1" min="1" max="1"/>
@@ -637,7 +637,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Tasks (Gantt + Resource Load): Task · Start Date · End Date · Progress · Group · Resource · Project</t>
+          <t>Tasks (Gantt + Resource Load): Task · Start Date · End Date · Group · Resource · Project</t>
         </is>
       </c>
     </row>
@@ -671,37 +671,44 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Gantt Resource well → Tasks[Resource]. Never put Project in the Resource well.</t>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>RAG + Progress on Projects is the portfolio health — not a second Progress on every task.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Progress is 0–100. RAG is Red / Amber / Green (or Rød / Gul / Grønn).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+          <t>Gantt Resource well → Tasks[Resource]. Never put Project in the Resource well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Task Progress is optional later for bar fill. Progress on Projects is 0–100. RAG: Red / Amber / Green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Put Task List on the page, click a project — Gantt and Resource Load follow.</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>https://datalund.no</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Free Power BI visuals · support@datalund.no</t>
         </is>
@@ -713,7 +720,7 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -912,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -942,20 +949,15 @@
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>Resource</t>
-        </is>
-      </c>
-      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
@@ -973,20 +975,17 @@
       <c r="C2" s="14" t="n">
         <v>46198</v>
       </c>
-      <c r="D2" s="13" t="n">
-        <v>100</v>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Ada Ng</t>
         </is>
       </c>
       <c r="F2" s="11" t="inlineStr">
-        <is>
-          <t>Ada Ng</t>
-        </is>
-      </c>
-      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>North Sea Hub</t>
         </is>
@@ -1004,20 +1003,17 @@
       <c r="C3" s="18" t="n">
         <v>46223</v>
       </c>
-      <c r="D3" s="17" t="n">
-        <v>75</v>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Sam Ortiz</t>
         </is>
       </c>
       <c r="F3" s="15" t="inlineStr">
-        <is>
-          <t>Sam Ortiz</t>
-        </is>
-      </c>
-      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>North Sea Hub</t>
         </is>
@@ -1035,20 +1031,17 @@
       <c r="C4" s="14" t="n">
         <v>46270</v>
       </c>
-      <c r="D4" s="13" t="n">
-        <v>20</v>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Ada Ng</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Ada Ng</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>North Sea Hub</t>
         </is>
@@ -1066,20 +1059,17 @@
       <c r="C5" s="18" t="n">
         <v>46254</v>
       </c>
-      <c r="D5" s="17" t="n">
-        <v>40</v>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Bo Berg</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>Bo Berg</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>Arctic Link</t>
         </is>
@@ -1097,20 +1087,17 @@
       <c r="C6" s="14" t="n">
         <v>46252</v>
       </c>
-      <c r="D6" s="13" t="n">
-        <v>0</v>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Riley Chen</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>Riley Chen</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Arctic Link</t>
         </is>
@@ -1128,20 +1115,17 @@
       <c r="C7" s="18" t="n">
         <v>46258</v>
       </c>
-      <c r="D7" s="17" t="n">
-        <v>0</v>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Bo Berg</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>Bo Berg</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>Arctic Link</t>
         </is>
@@ -1159,20 +1143,17 @@
       <c r="C8" s="14" t="n">
         <v>46228</v>
       </c>
-      <c r="D8" s="13" t="n">
-        <v>50</v>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Initiation</t>
+        </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Initiation</t>
+          <t>Cara Diaz</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>Cara Diaz</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>Yard Retrofit</t>
         </is>
@@ -1190,20 +1171,17 @@
       <c r="C9" s="18" t="n">
         <v>46246</v>
       </c>
-      <c r="D9" s="17" t="n">
-        <v>0</v>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Initiation</t>
+        </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>Initiation</t>
+          <t>Cara Diaz</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>Cara Diaz</t>
-        </is>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>Yard Retrofit</t>
         </is>
@@ -1221,20 +1199,17 @@
       <c r="C10" s="14" t="n">
         <v>46244</v>
       </c>
-      <c r="D10" s="13" t="n">
-        <v>85</v>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Sam Ortiz</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>Sam Ortiz</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Digital Twin v2</t>
         </is>
@@ -1252,20 +1227,17 @@
       <c r="C11" s="18" t="n">
         <v>46259</v>
       </c>
-      <c r="D11" s="17" t="n">
-        <v>30</v>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Ada Ng</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>Ada Ng</t>
-        </is>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>Digital Twin v2</t>
         </is>
@@ -1283,20 +1255,17 @@
       <c r="C12" s="14" t="n">
         <v>46296</v>
       </c>
-      <c r="D12" s="13" t="n">
-        <v>10</v>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Finn Olsen</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Finn Olsen</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Port Expansion</t>
         </is>
@@ -1314,27 +1283,24 @@
       <c r="C13" s="18" t="n">
         <v>46280</v>
       </c>
-      <c r="D13" s="17" t="n">
-        <v>5</v>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Jordan Lee</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>Jordan Lee</t>
-        </is>
-      </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
           <t>Port Expansion</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:F13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>